--- a/Reporte_Pedro.xlsx
+++ b/Reporte_Pedro.xlsx
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46177.78371296881</v>
+        <v>46190.74034190091</v>
       </c>
     </row>
   </sheetData>
